--- a/artfynd/A 41899-2026 artfynd.xlsx
+++ b/artfynd/A 41899-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137325499</v>
       </c>
       <c r="B2" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>137325501</v>
       </c>
       <c r="B3" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>137325673</v>
       </c>
       <c r="B4" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>137325680</v>
       </c>
       <c r="B5" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>137325498</v>
       </c>
       <c r="B6" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>137325500</v>
       </c>
       <c r="B7" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>137325676</v>
       </c>
       <c r="B8" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>137325689</v>
       </c>
       <c r="B10" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>137325677</v>
       </c>
       <c r="B11" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>137325678</v>
       </c>
       <c r="B12" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 41899-2026 artfynd.xlsx
+++ b/artfynd/A 41899-2026 artfynd.xlsx
@@ -1744,7 +1744,7 @@
         <v>137325677</v>
       </c>
       <c r="B11" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>137325678</v>
       </c>
       <c r="B12" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 41899-2026 artfynd.xlsx
+++ b/artfynd/A 41899-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137325499</v>
       </c>
       <c r="B2" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>137325501</v>
       </c>
       <c r="B3" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>137325673</v>
       </c>
       <c r="B4" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>137325680</v>
       </c>
       <c r="B5" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>137325498</v>
       </c>
       <c r="B6" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>137325500</v>
       </c>
       <c r="B7" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>137325676</v>
       </c>
       <c r="B8" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>137325689</v>
       </c>
       <c r="B10" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>137325677</v>
       </c>
       <c r="B11" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>137325678</v>
       </c>
       <c r="B12" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 41899-2026 artfynd.xlsx
+++ b/artfynd/A 41899-2026 artfynd.xlsx
@@ -1744,7 +1744,7 @@
         <v>137325677</v>
       </c>
       <c r="B11" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 41899-2026 artfynd.xlsx
+++ b/artfynd/A 41899-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137325499</v>
       </c>
       <c r="B2" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>137325501</v>
       </c>
       <c r="B3" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>137325673</v>
       </c>
       <c r="B4" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>137325677</v>
       </c>
       <c r="B11" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>137325678</v>
       </c>
       <c r="B12" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 41899-2026 artfynd.xlsx
+++ b/artfynd/A 41899-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137325499</v>
       </c>
       <c r="B2" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>137325501</v>
       </c>
       <c r="B3" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>137325673</v>
       </c>
       <c r="B4" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>137325677</v>
       </c>
       <c r="B11" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>137325678</v>
       </c>
       <c r="B12" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 41899-2026 artfynd.xlsx
+++ b/artfynd/A 41899-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137325499</v>
       </c>
       <c r="B2" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>137325501</v>
       </c>
       <c r="B3" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>137325673</v>
       </c>
       <c r="B4" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>137325677</v>
       </c>
       <c r="B11" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>137325678</v>
       </c>
       <c r="B12" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 41899-2026 artfynd.xlsx
+++ b/artfynd/A 41899-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137325499</v>
       </c>
       <c r="B2" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>137325501</v>
       </c>
       <c r="B3" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>137325673</v>
       </c>
       <c r="B4" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>137325680</v>
       </c>
       <c r="B5" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>137325498</v>
       </c>
       <c r="B6" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>137325500</v>
       </c>
       <c r="B7" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>137325676</v>
       </c>
       <c r="B8" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>137325689</v>
       </c>
       <c r="B10" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>137325677</v>
       </c>
       <c r="B11" t="n">
-        <v>111430</v>
+        <v>111436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>137325678</v>
       </c>
       <c r="B12" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
